--- a/diseases/d114/2000-2004.xlsx
+++ b/diseases/d114/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>184</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>3.554730239925938</v>
       </c>
@@ -1787,9 +1784,6 @@
       <c r="O7" t="n">
         <v>65</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>1.447381986596352</v>
       </c>
@@ -2331,9 +2325,6 @@
       <c r="O10" t="n">
         <v>213</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>4.114986636436004</v>
       </c>
@@ -2966,9 +2957,6 @@
       <c r="O13" t="n">
         <v>57</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>1.269242665169109</v>
       </c>
@@ -3510,9 +3498,6 @@
       <c r="O16" t="n">
         <v>241</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>4.655923846859516</v>
       </c>
@@ -4145,9 +4130,6 @@
       <c r="O19" t="n">
         <v>93</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>2.070869611591704</v>
       </c>
@@ -4689,9 +4671,6 @@
       <c r="O22" t="n">
         <v>153</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>2.955835471242764</v>
       </c>
@@ -5324,9 +5303,6 @@
       <c r="O25" t="n">
         <v>106</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>2.360346008910974</v>
       </c>
@@ -5868,9 +5844,6 @@
       <c r="O28" t="n">
         <v>185</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>3.574049426012492</v>
       </c>
@@ -6503,9 +6476,6 @@
       <c r="O31" t="n">
         <v>104</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>2.315811178554163</v>
       </c>
@@ -7047,9 +7017,6 @@
       <c r="O34" t="n">
         <v>201</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>3.883156403397356</v>
       </c>
@@ -7682,9 +7649,6 @@
       <c r="O37" t="n">
         <v>79</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>1.759125799094028</v>
       </c>
@@ -8226,9 +8190,6 @@
       <c r="O40" t="n">
         <v>258</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>4.984350010330934</v>
       </c>
@@ -8861,9 +8822,6 @@
       <c r="O43" t="n">
         <v>150</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>3.340112276760812</v>
       </c>
@@ -9405,9 +9363,6 @@
       <c r="O46" t="n">
         <v>337</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>6.510565711168701</v>
       </c>
@@ -10040,9 +9995,6 @@
       <c r="O49" t="n">
         <v>220</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>4.898831339249192</v>
       </c>
@@ -10584,9 +10536,6 @@
       <c r="O52" t="n">
         <v>241</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>4.655923846859516</v>
       </c>
@@ -11219,9 +11168,6 @@
       <c r="O55" t="n">
         <v>243</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>5.410981888352516</v>
       </c>
@@ -11763,9 +11709,6 @@
       <c r="O58" t="n">
         <v>253</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>4.887754079898165</v>
       </c>
@@ -12398,9 +12341,6 @@
       <c r="O61" t="n">
         <v>140</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>3.117438124976759</v>
       </c>
@@ -12942,9 +12882,6 @@
       <c r="O64" t="n">
         <v>265</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>5.119584312936813</v>
       </c>
@@ -13577,9 +13514,6 @@
       <c r="O67" t="n">
         <v>105</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>2.338078593732569</v>
       </c>
@@ -14121,9 +14055,6 @@
       <c r="O70" t="n">
         <v>218</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>4.211582566868774</v>
       </c>
@@ -14756,9 +14687,6 @@
       <c r="O73" t="n">
         <v>112</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>2.493950499981407</v>
       </c>
@@ -15300,9 +15228,6 @@
       <c r="O76" t="n">
         <v>268</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>5.165796030856765</v>
       </c>
@@ -16174,9 +16099,6 @@
       <c r="O80" t="n">
         <v>79</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>1.750243760214832</v>
       </c>
@@ -16718,9 +16640,6 @@
       <c r="O83" t="n">
         <v>220</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>4.240578831300329</v>
       </c>
@@ -17353,9 +17272,6 @@
       <c r="O86" t="n">
         <v>91</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>2.016103571893035</v>
       </c>
@@ -17897,9 +17813,6 @@
       <c r="O89" t="n">
         <v>251</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>4.838114939347194</v>
       </c>
@@ -18532,9 +18445,6 @@
       <c r="O92" t="n">
         <v>115</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>2.54782319524944</v>
       </c>
@@ -19076,9 +18986,6 @@
       <c r="O95" t="n">
         <v>186</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>3.585216648281187</v>
       </c>
@@ -19711,9 +19618,6 @@
       <c r="O98" t="n">
         <v>177</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>3.921432222253486</v>
       </c>
@@ -20255,9 +20159,6 @@
       <c r="O101" t="n">
         <v>183</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>3.52739057330891</v>
       </c>
@@ -20890,9 +20791,6 @@
       <c r="O104" t="n">
         <v>95</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>2.104723509119102</v>
       </c>
@@ -21434,9 +21332,6 @@
       <c r="O107" t="n">
         <v>235</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>4.529709206161715</v>
       </c>
@@ -22069,9 +21964,6 @@
       <c r="O110" t="n">
         <v>123</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>2.725063069701575</v>
       </c>
@@ -22613,9 +22505,6 @@
       <c r="O113" t="n">
         <v>306</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>5.898259647172276</v>
       </c>
@@ -23248,9 +23137,6 @@
       <c r="O116" t="n">
         <v>197</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>4.364531908383823</v>
       </c>
@@ -23792,9 +23678,6 @@
       <c r="O119" t="n">
         <v>383</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>7.382462238127391</v>
       </c>
@@ -24427,9 +24310,6 @@
       <c r="O122" t="n">
         <v>287</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>6.35848049597034</v>
       </c>
@@ -24971,9 +24851,6 @@
       <c r="O125" t="n">
         <v>277</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>5.339274255773597</v>
       </c>
@@ -25606,9 +25483,6 @@
       <c r="O128" t="n">
         <v>263</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>5.826760872613936</v>
       </c>
@@ -26150,9 +26024,6 @@
       <c r="O131" t="n">
         <v>245</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>4.722462789402639</v>
       </c>
@@ -26785,9 +26656,6 @@
       <c r="O134" t="n">
         <v>273</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>6.048310715679104</v>
       </c>
@@ -27329,9 +27197,6 @@
       <c r="O137" t="n">
         <v>198</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>3.816520948170297</v>
       </c>
@@ -27964,9 +27829,6 @@
       <c r="O140" t="n">
         <v>129</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>2.857992975540676</v>
       </c>
@@ -28508,9 +28370,6 @@
       <c r="O143" t="n">
         <v>146</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>2.814202315317491</v>
       </c>
@@ -29143,9 +29002,6 @@
       <c r="O146" t="n">
         <v>76</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>1.683778807295282</v>
       </c>
@@ -29687,9 +29543,6 @@
       <c r="O149" t="n">
         <v>200</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>3.845750042399394</v>
       </c>
@@ -30561,9 +30414,6 @@
       <c r="O153" t="n">
         <v>85</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>1.873066059293779</v>
       </c>
@@ -31105,9 +30955,6 @@
       <c r="O156" t="n">
         <v>134</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>2.576652528407594</v>
       </c>
@@ -31740,9 +31587,6 @@
       <c r="O159" t="n">
         <v>78</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>1.718813560293115</v>
       </c>
@@ -32284,9 +32128,6 @@
       <c r="O162" t="n">
         <v>163</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>3.134286284555506</v>
       </c>
@@ -32919,9 +32760,6 @@
       <c r="O165" t="n">
         <v>117</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>2.578220340439672</v>
       </c>
@@ -33463,9 +33301,6 @@
       <c r="O168" t="n">
         <v>163</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>3.134286284555506</v>
       </c>
@@ -34098,9 +33933,6 @@
       <c r="O171" t="n">
         <v>77</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>1.696777489007306</v>
       </c>
@@ -34642,9 +34474,6 @@
       <c r="O174" t="n">
         <v>133</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>2.557423778195597</v>
       </c>
@@ -35277,9 +35106,6 @@
       <c r="O177" t="n">
         <v>57</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>1.256056063291122</v>
       </c>
@@ -35821,9 +35647,6 @@
       <c r="O180" t="n">
         <v>131</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>2.518966277771603</v>
       </c>
@@ -36456,9 +36279,6 @@
       <c r="O183" t="n">
         <v>103</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>2.269715342438344</v>
       </c>
@@ -37000,9 +36820,6 @@
       <c r="O186" t="n">
         <v>304</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>5.845540064447079</v>
       </c>
@@ -37635,9 +37452,6 @@
       <c r="O189" t="n">
         <v>173</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>3.812240332444986</v>
       </c>
@@ -38179,9 +37993,6 @@
       <c r="O192" t="n">
         <v>325</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>6.249343818899015</v>
       </c>
@@ -38814,9 +38625,6 @@
       <c r="O195" t="n">
         <v>248</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>5.464945678880674</v>
       </c>
@@ -39358,9 +39166,6 @@
       <c r="O198" t="n">
         <v>245</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>4.711043801939258</v>
       </c>
@@ -39993,9 +39798,6 @@
       <c r="O201" t="n">
         <v>205</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>4.517394613590879</v>
       </c>
@@ -40537,9 +40339,6 @@
       <c r="O204" t="n">
         <v>250</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>4.807187552999243</v>
       </c>
@@ -41172,9 +40971,6 @@
       <c r="O207" t="n">
         <v>170</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>3.746132118587558</v>
       </c>
@@ -41716,9 +41512,6 @@
       <c r="O210" t="n">
         <v>145</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>2.788168780739561</v>
       </c>
@@ -42351,9 +42144,6 @@
       <c r="O213" t="n">
         <v>106</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>2.335823556295772</v>
       </c>
@@ -42895,9 +42685,6 @@
       <c r="O216" t="n">
         <v>141</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>2.711253779891573</v>
       </c>
@@ -43530,9 +43317,6 @@
       <c r="O219" t="n">
         <v>80</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>1.762885702864733</v>
       </c>
@@ -44074,9 +43858,6 @@
       <c r="O222" t="n">
         <v>171</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>3.280289202573204</v>
       </c>
@@ -44948,9 +44729,6 @@
       <c r="O226" t="n">
         <v>66</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>1.445887971285541</v>
       </c>
@@ -45492,9 +45270,6 @@
       <c r="O229" t="n">
         <v>163</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>3.126825380230599</v>
       </c>
@@ -46127,9 +45902,6 @@
       <c r="O232" t="n">
         <v>70</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>1.533517545302847</v>
       </c>
@@ -46671,9 +46443,6 @@
       <c r="O235" t="n">
         <v>251</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>4.814927425999265</v>
       </c>
@@ -47306,9 +47075,6 @@
       <c r="O238" t="n">
         <v>84</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>1.840221054363416</v>
       </c>
@@ -47850,9 +47616,6 @@
       <c r="O241" t="n">
         <v>99</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>1.89911480148975</v>
       </c>
@@ -48485,9 +48248,6 @@
       <c r="O244" t="n">
         <v>87</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>1.905943234876395</v>
       </c>
@@ -49029,9 +48789,6 @@
       <c r="O247" t="n">
         <v>101</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>1.937480757075401</v>
       </c>
@@ -49664,9 +49421,6 @@
       <c r="O250" t="n">
         <v>73</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>1.599239725815826</v>
       </c>
@@ -50208,9 +49962,6 @@
       <c r="O253" t="n">
         <v>178</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>3.414570047122985</v>
       </c>
@@ -50843,9 +50594,6 @@
       <c r="O256" t="n">
         <v>76</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>1.664961906328805</v>
       </c>
@@ -51387,9 +51135,6 @@
       <c r="O259" t="n">
         <v>232</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>4.450450847935576</v>
       </c>
@@ -52022,9 +51767,6 @@
       <c r="O262" t="n">
         <v>194</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>4.250034339839318</v>
       </c>
@@ -52566,9 +52308,6 @@
       <c r="O265" t="n">
         <v>327</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>6.272833738254023</v>
       </c>
@@ -53201,9 +52940,6 @@
       <c r="O268" t="n">
         <v>268</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>5.87118145915947</v>
       </c>
@@ -53745,9 +53481,6 @@
       <c r="O271" t="n">
         <v>250</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>4.79574444820644</v>
       </c>
@@ -54380,9 +54113,6 @@
       <c r="O274" t="n">
         <v>245</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>5.367311408559964</v>
       </c>
@@ -54924,9 +54654,6 @@
       <c r="O277" t="n">
         <v>205</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>3.93251044752928</v>
       </c>
@@ -55559,9 +55286,6 @@
       <c r="O280" t="n">
         <v>182</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>3.987145617787402</v>
       </c>
@@ -56103,9 +55827,6 @@
       <c r="O283" t="n">
         <v>153</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>2.934995602302341</v>
       </c>
@@ -56738,9 +56459,6 @@
       <c r="O286" t="n">
         <v>100</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>2.190739350432638</v>
       </c>
@@ -57282,9 +57000,6 @@
       <c r="O289" t="n">
         <v>129</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>2.474604135274522</v>
       </c>
@@ -57917,9 +57632,6 @@
       <c r="O292" t="n">
         <v>81</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>1.774498873850437</v>
       </c>
@@ -58461,9 +58173,6 @@
       <c r="O295" t="n">
         <v>216</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>4.131482123306379</v>
       </c>
@@ -59335,9 +59044,6 @@
       <c r="O299" t="n">
         <v>80</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>1.742257977227599</v>
       </c>
@@ -59879,9 +59585,6 @@
       <c r="O302" t="n">
         <v>188</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>3.595919625840737</v>
       </c>
@@ -60514,9 +60217,6 @@
       <c r="O305" t="n">
         <v>70</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>1.524475730074149</v>
       </c>
@@ -61058,9 +60758,6 @@
       <c r="O308" t="n">
         <v>208</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>3.978464266887624</v>
       </c>
@@ -61693,9 +61390,6 @@
       <c r="O311" t="n">
         <v>99</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>2.156044246819154</v>
       </c>
@@ -62237,9 +61931,6 @@
       <c r="O314" t="n">
         <v>151</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>2.888212039903997</v>
       </c>
@@ -62872,9 +62563,6 @@
       <c r="O317" t="n">
         <v>106</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>2.308491819826569</v>
       </c>
@@ -63416,9 +63104,6 @@
       <c r="O320" t="n">
         <v>122</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>2.333522310386011</v>
       </c>
@@ -64051,9 +63736,6 @@
       <c r="O323" t="n">
         <v>80</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>1.742257977227599</v>
       </c>
@@ -64595,9 +64277,6 @@
       <c r="O326" t="n">
         <v>147</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>2.811703111694619</v>
       </c>
@@ -65230,9 +64909,6 @@
       <c r="O329" t="n">
         <v>79</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>1.720479752512254</v>
       </c>
@@ -65774,9 +65450,6 @@
       <c r="O332" t="n">
         <v>214</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>4.09322765920169</v>
       </c>
@@ -66409,9 +66082,6 @@
       <c r="O335" t="n">
         <v>182</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>3.963636898192788</v>
       </c>
@@ -66953,9 +66623,6 @@
       <c r="O338" t="n">
         <v>241</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>4.609662924614987</v>
       </c>
@@ -67588,9 +67255,6 @@
       <c r="O341" t="n">
         <v>263</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>5.727673100135733</v>
       </c>
@@ -68132,9 +67796,6 @@
       <c r="O344" t="n">
         <v>192</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>3.672428554050115</v>
       </c>
@@ -68767,9 +68428,6 @@
       <c r="O347" t="n">
         <v>168</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>3.658741752177959</v>
       </c>
@@ -69311,9 +68969,6 @@
       <c r="O350" t="n">
         <v>226</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>4.322754443829822</v>
       </c>
@@ -69946,9 +69601,6 @@
       <c r="O353" t="n">
         <v>213</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>4.638761864368483</v>
       </c>
@@ -70490,9 +70142,6 @@
       <c r="O356" t="n">
         <v>165</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>3.155993288636817</v>
       </c>
@@ -71125,9 +70774,6 @@
       <c r="O359" t="n">
         <v>178</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>3.876523999331408</v>
       </c>
@@ -71669,9 +71315,6 @@
       <c r="O362" t="n">
         <v>185</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>3.538537929683704</v>
       </c>
@@ -72303,9 +71946,6 @@
       </c>
       <c r="O365" t="n">
         <v>68</v>
-      </c>
-      <c r="Q365" t="n">
-        <v>0</v>
       </c>
       <c r="R365" t="n">
         <v>1.480919280643459</v>
